--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,10 +411,10 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 04/09 à 08/09/2026</v>
+        <v>Painel de Saldos Diários 08/09 à 09/09/2026</v>
       </c>
       <c r="C2" t="str">
-        <v>Plenaruis Reis e Mariano</v>
+        <v>Master Educação Profissional</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>142339.23</v>
+        <v>126277.66</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>142339.23</v>
+        <v>126277.66</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>2501.76</v>
+        <v>11380.55</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>2501.76</v>
+        <v>11380.55</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>269.22</v>
+        <v>269.32</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>269.22</v>
+        <v>269.32</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>126277.66</v>
+        <v>120678.74</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>126277.66</v>
+        <v>120678.74</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>11380.55</v>
+        <v>1889.65</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>11380.55</v>
+        <v>1889.65</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>269.32</v>
+        <v>269.42</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>269.32</v>
+        <v>269.42</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 08/09 à 09/09/2026</v>
+        <v>Painel de Saldos Diários 09/09 à 10/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 09/09 à 10/09/2026</v>
+        <v>Painel de Saldos Diários 10/09 à 11/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>120678.74</v>
+        <v>119278.99</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1400.57</v>
       </c>
     </row>
     <row r="6">
@@ -455,7 +455,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="7">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>120678.74</v>
+        <v>117442.56000000001</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>1889.65</v>
+        <v>2299.01</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>1889.65</v>
+        <v>2299.01</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>269.42</v>
+        <v>269.54</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>269.42</v>
+        <v>269.54</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 10/09 à 11/09/2026</v>
+        <v>Painel de Saldos Diários 11/09 à 14/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>119278.99</v>
+        <v>109437.9</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>1400.57</v>
+        <v>489.29</v>
       </c>
     </row>
     <row r="6">
@@ -455,7 +455,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C6">
-        <v>3237</v>
+        <v>5183</v>
       </c>
     </row>
     <row r="7">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>117442.56000000001</v>
+        <v>104744.18999999999</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>2299.01</v>
+        <v>14760.01</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>2299.01</v>
+        <v>14760.01</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>269.54</v>
+        <v>247.06</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>269.54</v>
+        <v>247.06</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 11/09 à 14/09/2026</v>
+        <v>Painel de Saldos Diários 14/09 à 15/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>109437.9</v>
+        <v>69985.86</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>489.29</v>
+        <v>2974.76</v>
       </c>
     </row>
     <row r="6">
@@ -455,7 +455,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C6">
-        <v>5183</v>
+        <v>2263.24</v>
       </c>
     </row>
     <row r="7">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>104744.18999999999</v>
+        <v>70697.37999999999</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>14760.01</v>
+        <v>6723.75</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>14760.01</v>
+        <v>6723.75</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>247.06</v>
+        <v>269.75</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>247.06</v>
+        <v>269.75</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 14/09 à 15/09/2026</v>
+        <v>Painel de Saldos Diários 16/09 à 17/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>69985.86</v>
+        <v>68165.37</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>2974.76</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="6">
@@ -455,7 +455,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C6">
-        <v>2263.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>70697.37999999999</v>
+        <v>68169.58</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>6723.75</v>
+        <v>-4002.84</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>6723.75</v>
+        <v>-4002.84</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>269.75</v>
+        <v>247.06</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>269.75</v>
+        <v>247.06</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 16/09 à 17/09/2026</v>
+        <v>Painel de Saldos Diários 18/09 à 21/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>68165.37</v>
+        <v>53061</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>4.21</v>
+        <v>3215.76</v>
       </c>
     </row>
     <row r="6">
@@ -455,7 +455,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>2646.7</v>
       </c>
     </row>
     <row r="7">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>68169.58</v>
+        <v>53630.060000000005</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>-4002.84</v>
+        <v>6252.68</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>-4002.84</v>
+        <v>6252.68</v>
       </c>
     </row>
     <row r="13">

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 18/09 à 21/09/2026</v>
+        <v>Painel de Saldos Diários 21/09 à 22/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>53061</v>
+        <v>53626.35</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>3215.76</v>
+        <v>244.11</v>
       </c>
     </row>
     <row r="6">
@@ -455,7 +455,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C6">
-        <v>2646.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>53630.060000000005</v>
+        <v>53870.46</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>6252.68</v>
+        <v>13308.79</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>6252.68</v>
+        <v>13308.79</v>
       </c>
     </row>
     <row r="13">

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 21/09 à 22/09/2026</v>
+        <v>Painel de Saldos Diários 23/09 à 24/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>53626.35</v>
+        <v>54590.43</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>244.11</v>
+        <v>2924.5</v>
       </c>
     </row>
     <row r="6">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>53870.46</v>
+        <v>57514.93</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>13308.79</v>
+        <v>13164.32</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>13308.79</v>
+        <v>13164.32</v>
       </c>
     </row>
     <row r="13">

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 23/09 à 24/09/2026</v>
+        <v>Painel de Saldos Diários 24/09 à 25/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>54590.43</v>
+        <v>57656.21</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>2924.5</v>
+        <v>2745.25</v>
       </c>
     </row>
     <row r="6">
@@ -455,7 +455,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>13902.27</v>
       </c>
     </row>
     <row r="7">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>57514.93</v>
+        <v>46499.19</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>13164.32</v>
+        <v>2647.64</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1218.42</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +507,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>781.1700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>13164.32</v>
+        <v>3084.89</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>247.06</v>
+        <v>270.61</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>247.06</v>
+        <v>270.61</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 24/09 à 25/09/2026</v>
+        <v>Painel de Saldos Diários 25/09 à 28/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>57656.21</v>
+        <v>43928.99</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>2745.25</v>
+        <v>8311.51</v>
       </c>
     </row>
     <row r="6">
@@ -455,7 +455,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C6">
-        <v>13902.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>46499.19</v>
+        <v>52240.5</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>2647.64</v>
+        <v>17893.47</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C10">
-        <v>1218.42</v>
+        <v>11170.55</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +507,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C11">
-        <v>781.1700000000001</v>
+        <v>10497.86</v>
       </c>
     </row>
     <row r="12">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>3084.89</v>
+        <v>18566.16</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>270.61</v>
+        <v>270.71</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>270.61</v>
+        <v>270.71</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 25/09 à 28/09/2026</v>
+        <v>Painel de Saldos Diários 28/09 à 29/09/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>43928.99</v>
+        <v>52235.98</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>8311.51</v>
+        <v>7055.41</v>
       </c>
     </row>
     <row r="6">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>52240.5</v>
+        <v>59291.39</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>17893.47</v>
+        <v>18532.13</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C10">
-        <v>11170.55</v>
+        <v>405.33</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +507,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C11">
-        <v>10497.86</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="12">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>18566.16</v>
+        <v>18935.530000000002</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>270.71</v>
+        <v>270.82</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>270.71</v>
+        <v>270.82</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 28/09 à 29/09/2026</v>
+        <v>Painel de Saldos Diários 01/10 à 02/10/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>52235.98</v>
+        <v>57149.52</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>7055.41</v>
+        <v>3720.1000000000004</v>
       </c>
     </row>
     <row r="6">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>59291.39</v>
+        <v>60869.619999999995</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>18532.13</v>
+        <v>10974.63</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C10">
-        <v>405.33</v>
+        <v>887.78</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +507,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C11">
-        <v>1.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>18935.530000000002</v>
+        <v>11862.41</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>270.82</v>
+        <v>271.14</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>270.82</v>
+        <v>271.14</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 07/10 à 08/10/2026</v>
+        <v>Painel de Saldos Diários 15/10 à 16/10/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>42193.45</v>
+        <v>28025.14</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>436.66</v>
+        <v>1172.1100000000001</v>
       </c>
     </row>
     <row r="6">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>42630.11</v>
+        <v>29197.25</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>23769.87</v>
+        <v>-5398.01</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C10">
-        <v>1442</v>
+        <v>1207.53</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +507,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C11">
-        <v>132.63</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>25079.239999999998</v>
+        <v>-4597.4800000000005</v>
       </c>
     </row>
     <row r="13">
@@ -537,7 +537,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C14">
-        <v>423.79</v>
+        <v>343.36</v>
       </c>
     </row>
     <row r="15">
@@ -570,7 +570,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C17">
-        <v>423.79</v>
+        <v>343.36</v>
       </c>
     </row>
     <row r="18">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>271.56</v>
+        <v>272.1</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>271.56</v>
+        <v>272.1</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 15/10 à 16/10/2026</v>
+        <v>Painel de Saldos Diários 21/10 à 22/10/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>28025.14</v>
+        <v>16185.07</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>1172.1100000000001</v>
+        <v>1722.32</v>
       </c>
     </row>
     <row r="6">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>29197.25</v>
+        <v>17907.39</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>-5398.01</v>
+        <v>6407.62</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C10">
-        <v>1207.53</v>
+        <v>2022.01</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +507,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C11">
-        <v>407</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="12">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>-4597.4800000000005</v>
+        <v>8423.839999999998</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>272.1</v>
+        <v>272.53</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>272.1</v>
+        <v>272.53</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 21/10 à 22/10/2026</v>
+        <v>Painel de Saldos Diários 22/10 à 23/10/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>16185.07</v>
+        <v>17907.07</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>1722.32</v>
+        <v>5072.17</v>
       </c>
     </row>
     <row r="6">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>17907.39</v>
+        <v>22979.239999999998</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>6407.62</v>
+        <v>10151.71</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C10">
-        <v>2022.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +507,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C11">
-        <v>5.79</v>
+        <v>8025</v>
       </c>
     </row>
     <row r="12">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>8423.839999999998</v>
+        <v>2126.709999999999</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>272.53</v>
+        <v>272.64</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>272.53</v>
+        <v>272.64</v>
       </c>
     </row>
   </sheetData>

--- a/painel-de-saldos.xlsx
+++ b/painel-de-saldos.xlsx
@@ -411,7 +411,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Painel de Saldos Diários 28/10 à 29/10/2026</v>
+        <v>Painel de Saldos Diários 29/10 à 30/10/2026</v>
       </c>
       <c r="C2" t="str">
         <v>Master Educação Profissional</v>
@@ -433,7 +433,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C4">
-        <v>41941.41</v>
+        <v>63479.39</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C5">
-        <v>283.83</v>
+        <v>485.38</v>
       </c>
     </row>
     <row r="6">
@@ -455,7 +455,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C6">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -466,7 +466,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C7">
-        <v>41225.240000000005</v>
+        <v>63964.77</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C9">
-        <v>-676.05</v>
+        <v>-1776.16</v>
       </c>
     </row>
     <row r="10">
@@ -496,7 +496,7 @@
         <v xml:space="preserve">Entrada  ( B ) </v>
       </c>
       <c r="C10">
-        <v>1265.5</v>
+        <v>805.11</v>
       </c>
     </row>
     <row r="11">
@@ -507,7 +507,7 @@
         <v xml:space="preserve">Saída ( C ) </v>
       </c>
       <c r="C11">
-        <v>1.93</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="12">
@@ -518,7 +518,7 @@
         <v xml:space="preserve">Saldo Atual ( A + B - C ) </v>
       </c>
       <c r="C12">
-        <v>587.5200000000001</v>
+        <v>-996.1400000000001</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         <v xml:space="preserve">Saldo Anterior ( A ) </v>
       </c>
       <c r="C19">
-        <v>273.06</v>
+        <v>273.18</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
         <v xml:space="preserve">Saldo Atual da Conta de Aplicação </v>
       </c>
       <c r="C22">
-        <v>273.06</v>
+        <v>273.18</v>
       </c>
     </row>
   </sheetData>
